--- a/assets/art/enemies/bosses/enm_boss_monitor002/source/boss002_production_ledger.xlsx
+++ b/assets/art/enemies/bosses/enm_boss_monitor002/source/boss002_production_ledger.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>T Pose骨骼蒙皮；模型/动作双母版；六表情状态</t>
+          <t>v009握持待机/16节垂线/3材质双母版</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>手端控制骨驱动伸缩；线圈半径保持</t>
+          <t>每臂6段FK；idle下垂；stretch_L/R控制长度</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4指两节骨蒙皮，每手1拇指+3手指</t>
+          <t>四指握持+平滑蒙皮：左手夹键盘、右手握线</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5节数据线骨链</t>
+          <t>16节数据线骨链；自然下垂线环，插头朝下</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3段柔性支撑蒙皮；底座固定</t>
+          <t>3段柔性支撑延伸到屏幕中心后轴</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>v005</t>
+          <t>v009</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>模型model_v005 + 动作animation_v005</t>
+          <t>模型model_v009 + 动作animation_v009</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18,308三角面</t>
+          <t>18,684三角面</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>source/rig_contract_v005.json</t>
+          <t>source/rig_contract_v009.json</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SKEL-MONITOR002-001</t>
+          <t>SKEL-MONITOR002-004</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>41骨，双母版同签名</t>
+          <t>63骨，双母版同签名；左右臂各6段</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,148 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>previews/rig_v005/audit.json</t>
+          <t>previews/idle_v009/audit.json</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21项通过；5个QA动作不是正式游戏动作</t>
+          <t>16项通过；正式idle；其他正式动画待制作</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>v006材质</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>共3个</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>身体色盘UV / 六表情共用图集 / 屏幕代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>v006控制</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>rear_axle / monitor_spin / arm_01..06.L/R</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>stretch_L/R伸缩；code_scroll正数向上滚动</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>v007材质</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>共3个</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>身体色盘UV / 六表情共用图集 / 屏幕代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>v007控制</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>rear_axle / monitor_spin / arm_01..06.L/R</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>stretch_L/R伸缩；code_scroll正数向上滚动</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>v008材质</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>共3个</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>身体色盘UV / 六表情共用图集 / 屏幕代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>v008控制</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>rear_axle / monitor_spin / arm_01..06.L/R</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>stretch_L/R伸缩；code_scroll正数向上滚动</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>v009材质</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>共3个</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>身体色盘UV / 六表情共用图集 / 屏幕代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>v009控制</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rear_axle / monitor_spin / arm_01..06.L/R</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>stretch_L/R伸缩；code_scroll正数向上滚动</t>
         </is>
       </c>
     </row>

--- a/assets/art/enemies/bosses/enm_boss_monitor002/source/boss002_production_ledger.xlsx
+++ b/assets/art/enemies/bosses/enm_boss_monitor002/source/boss002_production_ledger.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>v009握持待机/16节垂线/3材质双母版</t>
+          <t>v011握持待机/16节垂线/3材质双母版</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>v009</t>
+          <t>v011</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>模型model_v009 + 动作animation_v009</t>
+          <t>模型model_v011 + 动作animation_v011</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>source/rig_contract_v009.json</t>
+          <t>source/rig_contract_v011.json</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SKEL-MONITOR002-004</t>
+          <t>SKEL-MONITOR002-005</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>63骨，双母版同签名；左右臂各6段</t>
+          <t>64骨，双母版同签名；左右臂各6段</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>previews/idle_v009/audit.json</t>
+          <t>previews/move_v011/audit.json</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16项通过；正式idle；其他正式动画待制作</t>
+          <t>26项通过；正式idle；其他正式动画待制作</t>
         </is>
       </c>
     </row>
@@ -1010,6 +1010,74 @@
         </is>
       </c>
       <c r="C34" t="inlineStr">
+        <is>
+          <t>stretch_L/R伸缩；code_scroll正数向上滚动</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>v010材质</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>共3个</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>身体色盘UV / 六表情共用图集 / 屏幕代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>v010控制</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>rear_axle / monitor_spin / arm_01..06.L/R</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>stretch_L/R伸缩；code_scroll正数向上滚动</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>v011材质</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>共3个</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>身体色盘UV / 六表情共用图集 / 屏幕代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>v011控制</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>rear_axle / monitor_spin / arm_01..06.L/R</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>stretch_L/R伸缩；code_scroll正数向上滚动</t>
         </is>

--- a/assets/art/enemies/bosses/enm_boss_monitor002/source/boss002_production_ledger.xlsx
+++ b/assets/art/enemies/bosses/enm_boss_monitor002/source/boss002_production_ledger.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B4" t="str" s="2">
-        <v>v027 坐地眩晕反弹与接地电流</v>
+        <v>v029 击晕坐地双手摊地</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B20" t="str">
-        <v>v027</v>
+        <v>v029</v>
       </c>
       <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C20" t="str">
-        <v>model_v027 + animation_v027；v012/v013保留回退</v>
+        <v>model_v029 + animation_v029；v012/v013保留回退</v>
       </c>
     </row>
     <row r="21">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C21" t="str">
-        <v>source/rig_contract_v027.json</v>
+        <v>source/rig_contract_v029.json</v>
       </c>
     </row>
     <row r="22">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B26" t="str">
-        <v>previews/impact_electric_v027/audit.json</v>
+        <v>previews/seated_hands_v029/audit.json</v>
       </c>
       <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C26" t="str">
-        <v>v027 受击后坐地一次反弹并进入眩晕：螺旋眼、环绕星星、单帧黄色受击闪形；特殊攻击接地线缆增加随骨骼蓝色电流，拔出关闭。15动作，源级检查，未导出或接入Godot。</v>
+        <v>v029 击晕第二次坐地后双手张开摊地，弹簧臂松弛弯垂，键盘平放、数据线低放，眩晕循环保持，起身收回；只改stun三段，其他12段保持，未导出或接入Godot。</v>
       </c>
     </row>
     <row r="27">

--- a/assets/art/enemies/bosses/enm_boss_monitor002/source/boss002_production_ledger.xlsx
+++ b/assets/art/enemies/bosses/enm_boss_monitor002/source/boss002_production_ledger.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss002制作明细" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Boss002制作明细'!$A$10:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Boss002制作明细'!$A$10:$D$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,8 +494,10 @@
           <t>制作范围</t>
         </is>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B4" t="str" s="2">
-        <v>v031 正式资产/十二态/四技能/三阶段</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>v031 正式16剪辑/十二态/四技能/三阶段</t>
+        </is>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
@@ -764,11 +766,15 @@
           <t>当前源版本</t>
         </is>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B20" t="str" s="0">
-        <v>v031</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C20" t="str" s="0">
-        <v>assets/art/enemies/bosses/enm_boss_monitor002/source/enm_boss_monitor002_model_v031.blend; assets/art/enemies/bosses/enm_boss_monitor002/source/enm_boss_monitor002_animation_v031.blend</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>v031</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>assets/art/enemies/bosses/enm_boss_monitor002/source/enm_boss_monitor002_model_v031.blend; assets/art/enemies/bosses/enm_boss_monitor002/source/enm_boss_monitor002_animation_v031.blend</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -782,8 +788,10 @@
           <t>18,684三角面</t>
         </is>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C21" t="str" s="0">
-        <v>source/rig_contract_v031.json</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>source/rig_contract_v031.json</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -860,11 +868,15 @@
           <t>绑定验证</t>
         </is>
       </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B26" t="str" s="0">
-        <v>previews/runtime/flow_report.json</v>
-      </c>
-      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C26" t="str" s="0">
-        <v>v031正式接入：16源剪辑/64骨/十二态/四技能/三阶段；根驱动弹簧甩臂、双螺旋坐地、黄色单帧闪形及接地电流；507项专项及真实渲染10关键帧通过；Enemy3D拥有碰撞/AI/伤害；远征01 Boss房调用boss_monitor002。；asset_guard分类：version_increment。</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>previews/runtime/flow_report.json; previews/runtime/visual_report.json</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>恢复v031老版走路；底座23°侧翘、原横移与手臂节奏。其余15剪辑、四技能、三阶段与远征01投放不变。</t>
+        </is>
       </c>
     </row>
     <row r="27">
